--- a/data/Delstidue 1/Resultater_DS1_Origami.xlsx
+++ b/data/Delstidue 1/Resultater_DS1_Origami.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ramboll-my.sharepoint.com/personal/ahmad_rezaie_ramboll_no/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="49" documentId="8_{C64A8CAB-14C6-401B-A689-679E1038BF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BCFB2108-B2E8-4011-AA44-8AF70D55A709}"/>
+  <xr:revisionPtr revIDLastSave="54" documentId="8_{C64A8CAB-14C6-401B-A689-679E1038BF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EACB3A07-DF3E-4464-B567-6EE1ACA246AA}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31710" yWindow="-375" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rådata" sheetId="1" r:id="rId1"/>
@@ -683,45 +683,6 @@
   </cellStyleXfs>
   <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -892,6 +853,45 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1541,11 +1541,15 @@
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1732,1329 +1736,1327 @@
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
-    <col min="3" max="3" width="42" style="14" customWidth="1"/>
+    <col min="3" max="3" width="42" style="1" customWidth="1"/>
     <col min="4" max="11" width="10" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-      <c r="K1" s="13"/>
-      <c r="L1" s="15"/>
-      <c r="M1" s="15"/>
-      <c r="N1" s="15"/>
-      <c r="O1" s="15"/>
-      <c r="P1" s="15"/>
-      <c r="Q1" s="15"/>
-      <c r="R1" s="15"/>
-      <c r="S1" s="15"/>
-      <c r="T1" s="15"/>
-      <c r="U1" s="15"/>
-      <c r="V1" s="15"/>
-      <c r="W1" s="15"/>
-      <c r="X1" s="15"/>
-      <c r="Y1" s="15"/>
-      <c r="Z1" s="15"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
+      <c r="L1" s="2"/>
+      <c r="M1" s="2"/>
+      <c r="N1" s="2"/>
+      <c r="O1" s="2"/>
+      <c r="P1" s="2"/>
+      <c r="Q1" s="2"/>
+      <c r="R1" s="2"/>
+      <c r="S1" s="2"/>
+      <c r="T1" s="2"/>
+      <c r="U1" s="2"/>
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="16" t="s">
+      <c r="B2" s="65"/>
+      <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="17"/>
-      <c r="N2" s="17"/>
-      <c r="O2" s="17"/>
-      <c r="P2" s="17"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
+      <c r="O2" s="4"/>
+      <c r="P2" s="4"/>
     </row>
     <row r="3" spans="1:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="18"/>
-      <c r="B3" s="18"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="11" t="s">
+      <c r="A3" s="5"/>
+      <c r="B3" s="5"/>
+      <c r="C3" s="6"/>
+      <c r="D3" s="66" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="10" t="s">
+      <c r="E3" s="66"/>
+      <c r="F3" s="66"/>
+      <c r="G3" s="66"/>
+      <c r="H3" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="10"/>
-      <c r="J3" s="10"/>
-      <c r="K3" s="10"/>
+      <c r="I3" s="67"/>
+      <c r="J3" s="67"/>
+      <c r="K3" s="67"/>
     </row>
     <row r="4" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="20" t="s">
+      <c r="A4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="D4" s="22" t="s">
+      <c r="D4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="23" t="s">
+      <c r="E4" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="23" t="s">
+      <c r="F4" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="G4" s="23" t="s">
+      <c r="G4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="24" t="s">
+      <c r="H4" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="24" t="s">
+      <c r="I4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="J4" s="24" t="s">
+      <c r="J4" s="11" t="s">
         <v>10</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="11" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:26" s="25" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="9" t="s">
+    <row r="5" spans="1:26" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="68" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
+      <c r="B5" s="68"/>
+      <c r="C5" s="68"/>
+      <c r="D5" s="68"/>
+      <c r="E5" s="68"/>
+      <c r="F5" s="68"/>
+      <c r="G5" s="68"/>
+      <c r="H5" s="68"/>
+      <c r="I5" s="68"/>
+      <c r="J5" s="68"/>
+      <c r="K5" s="68"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A6" s="26" t="s">
+      <c r="A6" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="28" t="s">
+      <c r="C6" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="29" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="F6" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>16</v>
-      </c>
-      <c r="H6" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="J6" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="K6" s="31" t="s">
+      <c r="D6" s="16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="H6" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="J6" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="K6" s="18" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A7" s="32" t="s">
+      <c r="A7" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B7" s="33" t="s">
+      <c r="B7" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="C7" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="E7" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J7" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K7" s="37" t="s">
+      <c r="D7" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F7" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J7" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K7" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="33" t="s">
+      <c r="B8" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="34" t="s">
+      <c r="C8" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G8" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="H8" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J8" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K8" s="37" t="s">
+      <c r="D8" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E8" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F8" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J8" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K8" s="24" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="32" t="s">
+      <c r="A9" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B9" s="33" t="s">
+      <c r="B9" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="34" t="s">
+      <c r="C9" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D9" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G9" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="H9" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="J9" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K9" s="37" t="s">
+      <c r="D9" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F9" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H9" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="J9" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K9" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="33" t="s">
+      <c r="B10" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="34" t="s">
+      <c r="C10" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D10" s="35" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G10" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="H10" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="I10" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J10" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K10" s="37" t="s">
+      <c r="D10" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H10" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="I10" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J10" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K10" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="A11" s="32" t="s">
+      <c r="A11" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="33" t="s">
+      <c r="B11" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="34" t="s">
+      <c r="C11" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="D11" s="35" t="s">
-        <v>20</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F11" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G11" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="H11" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="J11" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K11" s="37" t="s">
+      <c r="D11" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G11" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H11" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" s="24" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="32" t="s">
+      <c r="A12" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="E12" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="H12" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J12" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K12" s="37" t="s">
+      <c r="D12" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E12" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H12" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+      <c r="A13" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="8"/>
-      <c r="C13" s="8"/>
-      <c r="D13" s="39">
+      <c r="B13" s="69"/>
+      <c r="C13" s="69"/>
+      <c r="D13" s="26">
         <f t="shared" ref="D13:K13" si="0">COUNTIF(D6:D12,"J")</f>
         <v>4</v>
       </c>
-      <c r="E13" s="40">
+      <c r="E13" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="F13" s="40">
+      <c r="F13" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="G13" s="40">
+      <c r="G13" s="27">
         <f t="shared" si="0"/>
         <v>3</v>
       </c>
-      <c r="H13" s="40">
+      <c r="H13" s="27">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="I13" s="40">
+      <c r="I13" s="27">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="J13" s="40">
+      <c r="J13" s="27">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="K13" s="40">
+      <c r="K13" s="27">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="41">
+      <c r="B14" s="70"/>
+      <c r="C14" s="70"/>
+      <c r="D14" s="28">
         <f t="shared" ref="D14:K14" si="1">COUNTIF(D6:D12,"N")</f>
         <v>3</v>
       </c>
-      <c r="E14" s="42">
+      <c r="E14" s="29">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="F14" s="42">
+      <c r="F14" s="29">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="G14" s="42">
+      <c r="G14" s="29">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="H14" s="42">
+      <c r="H14" s="29">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="I14" s="42">
+      <c r="I14" s="29">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
-      <c r="J14" s="42">
+      <c r="J14" s="29">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K14" s="42">
+      <c r="K14" s="29">
         <f t="shared" si="1"/>
         <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="6"/>
-      <c r="C15" s="6"/>
-      <c r="D15" s="43">
+      <c r="B15" s="71"/>
+      <c r="C15" s="71"/>
+      <c r="D15" s="30">
         <v>7</v>
       </c>
-      <c r="E15" s="44" t="s">
+      <c r="E15" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="F15" s="44" t="s">
+      <c r="F15" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="G15" s="44" t="s">
+      <c r="G15" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="H15" s="44" t="s">
+      <c r="H15" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="I15" s="44" t="s">
+      <c r="I15" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="J15" s="44" t="s">
+      <c r="J15" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="K15" s="44" t="s">
+      <c r="K15" s="31" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="6"/>
-      <c r="C16" s="6"/>
-      <c r="D16" s="45">
+      <c r="B16" s="71"/>
+      <c r="C16" s="71"/>
+      <c r="D16" s="32">
         <f t="shared" ref="D16:K16" si="2">IFERROR(D13/D15,0)</f>
         <v>0.5714285714285714</v>
       </c>
-      <c r="E16" s="46">
+      <c r="E16" s="33">
         <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="F16" s="46">
+      <c r="F16" s="33">
         <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="G16" s="46">
+      <c r="G16" s="33">
         <f t="shared" si="2"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="H16" s="46">
+      <c r="H16" s="33">
         <f t="shared" si="2"/>
         <v>0.8571428571428571</v>
       </c>
-      <c r="I16" s="46">
+      <c r="I16" s="33">
         <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
-      <c r="J16" s="46">
+      <c r="J16" s="33">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
-      <c r="K16" s="46">
+      <c r="K16" s="33">
         <f t="shared" si="2"/>
         <v>0.7142857142857143</v>
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="9" t="s">
+      <c r="A18" s="68" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="9"/>
-      <c r="E18" s="9"/>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9"/>
-      <c r="H18" s="9"/>
-      <c r="I18" s="9"/>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
+      <c r="B18" s="68"/>
+      <c r="C18" s="68"/>
+      <c r="D18" s="68"/>
+      <c r="E18" s="68"/>
+      <c r="F18" s="68"/>
+      <c r="G18" s="68"/>
+      <c r="H18" s="68"/>
+      <c r="I18" s="68"/>
+      <c r="J18" s="68"/>
+      <c r="K18" s="68"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="47" t="s">
+      <c r="A19" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="B19" s="48" t="s">
+      <c r="B19" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="49" t="s">
+      <c r="C19" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="D19" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F19" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G19" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="H19" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J19" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K19" s="37" t="s">
+      <c r="D19" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E19" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G19" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H19" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J19" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K19" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="47" t="s">
+      <c r="A20" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="B20" s="48" t="s">
+      <c r="B20" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="49" t="s">
+      <c r="C20" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="D20" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="F20" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="G20" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="H20" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J20" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K20" s="37" t="s">
+      <c r="D20" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F20" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G20" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H20" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J20" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K20" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="47" t="s">
+      <c r="A21" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B21" s="48" t="s">
+      <c r="B21" s="35" t="s">
         <v>22</v>
       </c>
-      <c r="C21" s="49" t="s">
+      <c r="C21" s="36" t="s">
         <v>23</v>
       </c>
-      <c r="D21" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E21" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F21" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G21" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="H21" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J21" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K21" s="37" t="s">
+      <c r="D21" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E21" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F21" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H21" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J21" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K21" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="47" t="s">
+      <c r="A22" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="48" t="s">
+      <c r="B22" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="49" t="s">
+      <c r="C22" s="36" t="s">
         <v>25</v>
       </c>
-      <c r="D22" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="F22" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G22" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J22" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K22" s="37" t="s">
+      <c r="D22" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F22" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J22" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K22" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="47" t="s">
+      <c r="A23" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="48" t="s">
+      <c r="B23" s="35" t="s">
         <v>26</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="36" t="s">
         <v>27</v>
       </c>
-      <c r="D23" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F23" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G23" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="H23" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J23" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K23" s="37" t="s">
+      <c r="D23" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F23" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G23" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H23" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J23" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K23" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="47" t="s">
+      <c r="A24" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B24" s="48" t="s">
+      <c r="B24" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="C24" s="49" t="s">
+      <c r="C24" s="36" t="s">
         <v>29</v>
       </c>
-      <c r="D24" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="E24" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F24" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G24" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="H24" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J24" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K24" s="37" t="s">
+      <c r="D24" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F24" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G24" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J24" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K24" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="47" t="s">
+      <c r="A25" s="34" t="s">
         <v>21</v>
       </c>
-      <c r="B25" s="48" t="s">
+      <c r="B25" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="C25" s="49" t="s">
+      <c r="C25" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="D25" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="E25" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="F25" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="G25" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J25" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K25" s="37" t="s">
+      <c r="D25" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F25" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G25" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H25" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J25" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K25" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8" t="s">
+      <c r="A26" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="8"/>
-      <c r="C26" s="8"/>
-      <c r="D26" s="39">
+      <c r="B26" s="69"/>
+      <c r="C26" s="69"/>
+      <c r="D26" s="26">
         <f t="shared" ref="D26:K26" si="3">COUNTIF(D19:D25,"J")</f>
         <v>3</v>
       </c>
-      <c r="E26" s="40">
+      <c r="E26" s="27">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="F26" s="40">
+      <c r="F26" s="27">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
-      <c r="G26" s="40">
+      <c r="G26" s="27">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
-      <c r="H26" s="40">
+      <c r="H26" s="27">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="I26" s="40">
+      <c r="I26" s="27">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="J26" s="40">
+      <c r="J26" s="27">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
-      <c r="K26" s="40">
+      <c r="K26" s="27">
         <f t="shared" si="3"/>
         <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="7" t="s">
+      <c r="A27" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="41">
+      <c r="B27" s="70"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="28">
         <f t="shared" ref="D27:K27" si="4">COUNTIF(D19:D25,"N")</f>
         <v>4</v>
       </c>
-      <c r="E27" s="42">
+      <c r="E27" s="29">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="F27" s="42">
+      <c r="F27" s="29">
         <f t="shared" si="4"/>
         <v>5</v>
       </c>
-      <c r="G27" s="42">
+      <c r="G27" s="29">
         <f t="shared" si="4"/>
         <v>4</v>
       </c>
-      <c r="H27" s="42">
+      <c r="H27" s="29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I27" s="42">
+      <c r="I27" s="29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="J27" s="42">
+      <c r="J27" s="29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="K27" s="42">
+      <c r="K27" s="29">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="6" t="s">
+      <c r="A28" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="43" t="s">
+      <c r="B28" s="71"/>
+      <c r="C28" s="71"/>
+      <c r="D28" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="44" t="s">
+      <c r="E28" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="F28" s="44" t="s">
+      <c r="F28" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="G28" s="44" t="s">
+      <c r="G28" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="H28" s="44" t="s">
+      <c r="H28" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="I28" s="44" t="s">
+      <c r="I28" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="J28" s="44" t="s">
+      <c r="J28" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="K28" s="44" t="s">
+      <c r="K28" s="31" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="A29" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="45">
+      <c r="B29" s="71"/>
+      <c r="C29" s="71"/>
+      <c r="D29" s="32">
         <f t="shared" ref="D29:K29" si="5">IFERROR(D26/D28,0)</f>
         <v>0.42857142857142855</v>
       </c>
-      <c r="E29" s="46">
+      <c r="E29" s="33">
         <f t="shared" si="5"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="F29" s="46">
+      <c r="F29" s="33">
         <f t="shared" si="5"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="G29" s="46">
+      <c r="G29" s="33">
         <f t="shared" si="5"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="H29" s="46">
+      <c r="H29" s="33">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I29" s="46">
+      <c r="I29" s="33">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="J29" s="46">
+      <c r="J29" s="33">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="K29" s="46">
+      <c r="K29" s="33">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="9" t="s">
+      <c r="A31" s="68" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="9"/>
-      <c r="E31" s="9"/>
-      <c r="F31" s="9"/>
-      <c r="G31" s="9"/>
-      <c r="H31" s="9"/>
-      <c r="I31" s="9"/>
-      <c r="J31" s="9"/>
-      <c r="K31" s="9"/>
+      <c r="B31" s="68"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="68"/>
+      <c r="H31" s="68"/>
+      <c r="I31" s="68"/>
+      <c r="J31" s="68"/>
+      <c r="K31" s="68"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="B32" s="33" t="s">
+      <c r="B32" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="34" t="s">
+      <c r="C32" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D32" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F32" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="G32" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="H32" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J32" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K32" s="37" t="s">
+      <c r="D32" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E32" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F32" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G32" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H32" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J32" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K32" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="32" t="s">
+      <c r="A33" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="B33" s="33" t="s">
+      <c r="B33" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="C33" s="34" t="s">
+      <c r="C33" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="D33" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="F33" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="G33" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="H33" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J33" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K33" s="37" t="s">
+      <c r="D33" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E33" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G33" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H33" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J33" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K33" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="32" t="s">
+      <c r="A34" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="33" t="s">
+      <c r="B34" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="C34" s="34" t="s">
+      <c r="C34" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="D34" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E34" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F34" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G34" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="H34" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" s="37" t="s">
-        <v>20</v>
-      </c>
-      <c r="J34" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K34" s="37" t="s">
+      <c r="D34" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F34" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G34" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H34" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="24" t="s">
+        <v>20</v>
+      </c>
+      <c r="J34" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K34" s="24" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="35" spans="1:11" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="32" t="s">
+      <c r="A35" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="33" t="s">
+      <c r="B35" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="34" t="s">
+      <c r="C35" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="D35" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E35" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F35" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G35" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="H35" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J35" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K35" s="37" t="s">
+      <c r="D35" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E35" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F35" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G35" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H35" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J35" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K35" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="32" t="s">
+      <c r="A36" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="33" t="s">
+      <c r="B36" s="20" t="s">
         <v>26</v>
       </c>
-      <c r="C36" s="34" t="s">
+      <c r="C36" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="D36" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F36" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G36" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="H36" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I36" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J36" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K36" s="37" t="s">
+      <c r="D36" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E36" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F36" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G36" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H36" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J36" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K36" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="32" t="s">
+      <c r="A37" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B37" s="33" t="s">
+      <c r="B37" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="C37" s="34" t="s">
+      <c r="C37" s="21" t="s">
         <v>29</v>
       </c>
-      <c r="D37" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E37" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="F37" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="G37" s="36" t="s">
-        <v>20</v>
-      </c>
-      <c r="H37" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I37" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J37" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K37" s="37" t="s">
+      <c r="D37" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E37" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="F37" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="23" t="s">
+        <v>20</v>
+      </c>
+      <c r="H37" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J37" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K37" s="24" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="38" spans="1:11" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="32" t="s">
+      <c r="A38" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="B38" s="33" t="s">
+      <c r="B38" s="20" t="s">
         <v>30</v>
       </c>
-      <c r="C38" s="34" t="s">
+      <c r="C38" s="21" t="s">
         <v>31</v>
       </c>
-      <c r="D38" s="38" t="s">
-        <v>20</v>
-      </c>
-      <c r="E38" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="F38" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="G38" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="H38" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="I38" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="J38" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="K38" s="37" t="s">
+      <c r="D38" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="E38" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F38" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="G38" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="H38" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="J38" s="24" t="s">
+        <v>16</v>
+      </c>
+      <c r="K38" s="24" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8" t="s">
+      <c r="A39" s="69" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="8"/>
-      <c r="C39" s="8"/>
-      <c r="D39" s="39">
-        <f t="shared" ref="D39:K39" si="6">COUNTIF(D32:D38,"J")</f>
-        <v>0</v>
-      </c>
-      <c r="E39" s="40">
+      <c r="B39" s="69"/>
+      <c r="C39" s="69"/>
+      <c r="D39" s="26">
+        <v>1</v>
+      </c>
+      <c r="E39" s="27">
+        <f t="shared" ref="D39:K39" si="6">COUNTIF(E32:E38,"J")</f>
+        <v>2</v>
+      </c>
+      <c r="F39" s="27">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="G39" s="27">
         <f t="shared" si="6"/>
         <v>2</v>
       </c>
-      <c r="F39" s="40">
-        <f t="shared" si="6"/>
-        <v>3</v>
-      </c>
-      <c r="G39" s="40">
-        <f t="shared" si="6"/>
-        <v>2</v>
-      </c>
-      <c r="H39" s="40">
+      <c r="H39" s="27">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="I39" s="40">
+      <c r="I39" s="27">
         <f t="shared" si="6"/>
         <v>6</v>
       </c>
-      <c r="J39" s="40">
+      <c r="J39" s="27">
         <f t="shared" si="6"/>
         <v>7</v>
       </c>
-      <c r="K39" s="40">
+      <c r="K39" s="27">
         <f t="shared" si="6"/>
         <v>5</v>
       </c>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="7" t="s">
+      <c r="A40" s="70" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="41">
-        <f t="shared" ref="D40:K40" si="7">COUNTIF(D32:D38,"N")</f>
-        <v>7</v>
-      </c>
-      <c r="E40" s="42">
+      <c r="B40" s="70"/>
+      <c r="C40" s="70"/>
+      <c r="D40" s="28">
+        <v>6</v>
+      </c>
+      <c r="E40" s="29">
+        <f t="shared" ref="D40:K40" si="7">COUNTIF(E32:E38,"N")</f>
+        <v>5</v>
+      </c>
+      <c r="F40" s="29">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="G40" s="29">
         <f t="shared" si="7"/>
         <v>5</v>
       </c>
-      <c r="F40" s="42">
-        <f t="shared" si="7"/>
-        <v>4</v>
-      </c>
-      <c r="G40" s="42">
-        <f t="shared" si="7"/>
-        <v>5</v>
-      </c>
-      <c r="H40" s="42">
+      <c r="H40" s="29">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="I40" s="42">
+      <c r="I40" s="29">
         <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="J40" s="42">
+      <c r="J40" s="29">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="K40" s="42">
+      <c r="K40" s="29">
         <f t="shared" si="7"/>
         <v>2</v>
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="6" t="s">
+      <c r="A41" s="71" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="6"/>
-      <c r="C41" s="6"/>
-      <c r="D41" s="43" t="s">
+      <c r="B41" s="71"/>
+      <c r="C41" s="71"/>
+      <c r="D41" s="30" t="s">
         <v>30</v>
       </c>
-      <c r="E41" s="44" t="s">
+      <c r="E41" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="F41" s="44" t="s">
+      <c r="F41" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="G41" s="44" t="s">
+      <c r="G41" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="H41" s="44" t="s">
+      <c r="H41" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="I41" s="44" t="s">
+      <c r="I41" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="J41" s="44" t="s">
+      <c r="J41" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="K41" s="44" t="s">
+      <c r="K41" s="31" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
+      <c r="A42" s="71" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="45">
+      <c r="B42" s="71"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="32">
         <f t="shared" ref="D42:K42" si="8">IFERROR(D39/D41,0)</f>
-        <v>0</v>
-      </c>
-      <c r="E42" s="46">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="E42" s="33">
         <f t="shared" si="8"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="F42" s="46">
+      <c r="F42" s="33">
         <f t="shared" si="8"/>
         <v>0.42857142857142855</v>
       </c>
-      <c r="G42" s="46">
+      <c r="G42" s="33">
         <f t="shared" si="8"/>
         <v>0.2857142857142857</v>
       </c>
-      <c r="H42" s="46">
+      <c r="H42" s="33">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="I42" s="46">
+      <c r="I42" s="33">
         <f t="shared" si="8"/>
         <v>0.8571428571428571</v>
       </c>
-      <c r="J42" s="46">
+      <c r="J42" s="33">
         <f t="shared" si="8"/>
         <v>1</v>
       </c>
-      <c r="K42" s="46">
+      <c r="K42" s="33">
         <f t="shared" si="8"/>
         <v>0.7142857142857143</v>
       </c>
@@ -3103,725 +3105,725 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="72" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
+      <c r="B1" s="72"/>
+      <c r="C1" s="72"/>
+      <c r="D1" s="72"/>
+      <c r="E1" s="72"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="72"/>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+      <c r="J1" s="72"/>
+      <c r="K1" s="72"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="66" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="11"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="11"/>
-      <c r="J2" s="11"/>
-      <c r="K2" s="11"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
+      <c r="D2" s="66"/>
+      <c r="E2" s="66"/>
+      <c r="F2" s="66"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+      <c r="J2" s="66"/>
+      <c r="K2" s="66"/>
     </row>
     <row r="3" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A3" s="50"/>
-      <c r="B3" s="50" t="s">
+      <c r="A3" s="37"/>
+      <c r="B3" s="37" t="s">
         <v>40</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="37" t="s">
         <v>41</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="37" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="50" t="s">
+      <c r="E3" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="50" t="s">
+      <c r="F3" s="37" t="s">
         <v>44</v>
       </c>
-      <c r="G3" s="50" t="s">
+      <c r="G3" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="H3" s="50" t="s">
+      <c r="H3" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="I3" s="50" t="s">
+      <c r="I3" s="37" t="s">
         <v>47</v>
       </c>
-      <c r="J3" s="50" t="s">
+      <c r="J3" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="K3" s="50" t="s">
+      <c r="K3" s="37" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52" t="s">
+      <c r="A4" s="38"/>
+      <c r="B4" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="C4" s="53" t="s">
+      <c r="C4" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="D4" s="74">
+      <c r="D4" s="61">
         <f>Rådata!D16</f>
         <v>0.5714285714285714</v>
       </c>
-      <c r="E4" s="74">
+      <c r="E4" s="61">
         <f>Rådata!E16</f>
         <v>0.42857142857142855</v>
       </c>
-      <c r="F4" s="74">
+      <c r="F4" s="61">
         <f>Rådata!F16</f>
         <v>0.42857142857142855</v>
       </c>
-      <c r="G4" s="74">
+      <c r="G4" s="61">
         <f>Rådata!G16</f>
         <v>0.42857142857142855</v>
       </c>
-      <c r="H4" s="70">
+      <c r="H4" s="57">
         <f>AVERAGE(D4:G4)</f>
         <v>0.4642857142857143</v>
       </c>
-      <c r="I4" s="40">
+      <c r="I4" s="27">
         <f>Rådata!D13+Rådata!E13+Rådata!F13+Rådata!G13</f>
         <v>13</v>
       </c>
-      <c r="J4" s="42">
+      <c r="J4" s="29">
         <f>Rådata!D14+Rådata!E14+Rådata!F14+Rådata!G14</f>
         <v>15</v>
       </c>
-      <c r="K4" s="44">
+      <c r="K4" s="31">
         <f>+I4+J4</f>
         <v>28</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="54"/>
-      <c r="B5" s="55" t="s">
+      <c r="A5" s="41"/>
+      <c r="B5" s="42" t="s">
         <v>50</v>
       </c>
-      <c r="C5" s="56" t="s">
+      <c r="C5" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="D5" s="75">
+      <c r="D5" s="62">
         <f>Rådata!H16</f>
         <v>0.8571428571428571</v>
       </c>
-      <c r="E5" s="75">
+      <c r="E5" s="62">
         <f>Rådata!I16</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="F5" s="75">
+      <c r="F5" s="62">
         <f>Rådata!J16</f>
         <v>1</v>
       </c>
-      <c r="G5" s="75">
+      <c r="G5" s="62">
         <f>Rådata!K16</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="H5" s="70">
+      <c r="H5" s="57">
         <f>AVERAGE(D5:G5)</f>
         <v>0.8214285714285714</v>
       </c>
-      <c r="I5" s="40">
+      <c r="I5" s="27">
         <f>Rådata!H13+Rådata!I13+Rådata!J13+Rådata!K13</f>
         <v>23</v>
       </c>
-      <c r="J5" s="42">
+      <c r="J5" s="29">
         <f>Rådata!H14+Rådata!I14+Rådata!J14+Rådata!K14</f>
         <v>5</v>
       </c>
-      <c r="K5" s="44">
+      <c r="K5" s="31">
         <f>+I5+J5</f>
         <v>28</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H6" s="71"/>
+      <c r="H6" s="58"/>
     </row>
     <row r="7" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
-      <c r="B7" s="52" t="s">
+      <c r="A7" s="38"/>
+      <c r="B7" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="C7" s="53" t="s">
+      <c r="C7" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="D7" s="74">
+      <c r="D7" s="61">
         <f>Rådata!D29</f>
         <v>0.42857142857142855</v>
       </c>
-      <c r="E7" s="74">
+      <c r="E7" s="61">
         <f>Rådata!E29</f>
         <v>0.42857142857142855</v>
       </c>
-      <c r="F7" s="74">
+      <c r="F7" s="61">
         <f>Rådata!F29</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="G7" s="74">
+      <c r="G7" s="61">
         <f>Rådata!G29</f>
         <v>0.42857142857142855</v>
       </c>
-      <c r="H7" s="70">
+      <c r="H7" s="57">
         <f>AVERAGE(D7:G7)</f>
         <v>0.39285714285714285</v>
       </c>
-      <c r="I7" s="40">
+      <c r="I7" s="27">
         <f>Rådata!D26+Rådata!E26+Rådata!F26+Rådata!G26</f>
         <v>11</v>
       </c>
-      <c r="J7" s="42">
+      <c r="J7" s="29">
         <f>Rådata!D27+Rådata!E27+Rådata!F27+Rådata!G27</f>
         <v>17</v>
       </c>
-      <c r="K7" s="44">
-        <f t="shared" ref="K6:K11" si="0">+I7+J7</f>
+      <c r="K7" s="31">
+        <f t="shared" ref="K7:K10" si="0">+I7+J7</f>
         <v>28</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="54"/>
-      <c r="B8" s="55" t="s">
+      <c r="A8" s="41"/>
+      <c r="B8" s="42" t="s">
         <v>53</v>
       </c>
-      <c r="C8" s="56" t="s">
+      <c r="C8" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="D8" s="75">
+      <c r="D8" s="62">
         <f>Rådata!H29</f>
         <v>1</v>
       </c>
-      <c r="E8" s="75">
+      <c r="E8" s="62">
         <f>Rådata!I29</f>
         <v>1</v>
       </c>
-      <c r="F8" s="75">
+      <c r="F8" s="62">
         <f>Rådata!J29</f>
         <v>1</v>
       </c>
-      <c r="G8" s="75">
+      <c r="G8" s="62">
         <f>Rådata!K29</f>
         <v>1</v>
       </c>
-      <c r="H8" s="70">
+      <c r="H8" s="57">
         <f>AVERAGE(D8:G8)</f>
         <v>1</v>
       </c>
-      <c r="I8" s="40">
+      <c r="I8" s="27">
         <f>Rådata!H26+Rådata!I26+Rådata!J26+Rådata!K26</f>
         <v>28</v>
       </c>
-      <c r="J8" s="42">
+      <c r="J8" s="29">
         <f>Rådata!H27+Rådata!I27+Rådata!J27+Rådata!K27</f>
         <v>0</v>
       </c>
-      <c r="K8" s="44">
+      <c r="K8" s="31">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H9" s="71"/>
+      <c r="H9" s="58"/>
     </row>
     <row r="10" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="51"/>
-      <c r="B10" s="52" t="s">
+      <c r="A10" s="38"/>
+      <c r="B10" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="C10" s="53" t="s">
+      <c r="C10" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="74">
+      <c r="D10" s="61">
         <f>Rådata!D42</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="74">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="E10" s="61">
         <f>Rådata!E42</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="F10" s="74">
+      <c r="F10" s="61">
         <f>Rådata!F42</f>
         <v>0.42857142857142855</v>
       </c>
-      <c r="G10" s="74">
+      <c r="G10" s="61">
         <f>Rådata!G42</f>
         <v>0.2857142857142857</v>
       </c>
-      <c r="H10" s="70">
+      <c r="H10" s="57">
         <f>AVERAGE(D10:G10)</f>
-        <v>0.24999999999999997</v>
-      </c>
-      <c r="I10" s="40">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="I10" s="27">
         <f>Rådata!D39+Rådata!E39+Rådata!F39+Rådata!G39</f>
-        <v>7</v>
-      </c>
-      <c r="J10" s="42">
+        <v>8</v>
+      </c>
+      <c r="J10" s="29">
         <f>Rådata!D40+Rådata!E40+Rådata!F40+Rådata!G40</f>
-        <v>21</v>
-      </c>
-      <c r="K10" s="44">
+        <v>20</v>
+      </c>
+      <c r="K10" s="31">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="54"/>
-      <c r="B11" s="55" t="s">
+      <c r="A11" s="41"/>
+      <c r="B11" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="C11" s="56" t="s">
+      <c r="C11" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="75">
+      <c r="D11" s="62">
         <f>Rådata!H42</f>
         <v>1</v>
       </c>
-      <c r="E11" s="75">
+      <c r="E11" s="62">
         <f>Rådata!I42</f>
         <v>0.8571428571428571</v>
       </c>
-      <c r="F11" s="75">
+      <c r="F11" s="62">
         <f>Rådata!J42</f>
         <v>1</v>
       </c>
-      <c r="G11" s="75">
+      <c r="G11" s="62">
         <f>Rådata!K42</f>
         <v>0.7142857142857143</v>
       </c>
-      <c r="H11" s="70">
+      <c r="H11" s="57">
         <f>AVERAGE(D11:G11)</f>
         <v>0.8928571428571429</v>
       </c>
-      <c r="I11" s="40">
+      <c r="I11" s="27">
         <f>Rådata!H39+Rådata!I39+Rådata!J39+Rådata!K39</f>
         <v>25</v>
       </c>
-      <c r="J11" s="42">
+      <c r="J11" s="29">
         <f>Rådata!H40+Rådata!I40+Rådata!J40+Rådata!K40</f>
         <v>3</v>
       </c>
-      <c r="K11" s="44">
+      <c r="K11" s="31">
         <f>+I11+J11</f>
         <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H12" s="71"/>
+      <c r="H12" s="58"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="H13" s="71"/>
+      <c r="H13" s="58"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="73" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
-      <c r="D14" s="4"/>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4"/>
-      <c r="H14" s="72"/>
-      <c r="I14" s="57"/>
-      <c r="J14" s="57"/>
-      <c r="K14" s="57"/>
+      <c r="B14" s="73"/>
+      <c r="C14" s="73"/>
+      <c r="D14" s="73"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="44"/>
+      <c r="J14" s="44"/>
+      <c r="K14" s="44"/>
     </row>
     <row r="15" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="51"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="53" t="s">
+      <c r="A15" s="38"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="40" t="s">
         <v>51</v>
       </c>
-      <c r="H15" s="73">
+      <c r="H15" s="60">
         <f>AVERAGE(H4,H7,H10)</f>
-        <v>0.36904761904761907</v>
+        <v>0.38095238095238093</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="54"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="56" t="s">
+      <c r="A16" s="41"/>
+      <c r="B16" s="41"/>
+      <c r="C16" s="43" t="s">
         <v>52</v>
       </c>
-      <c r="H16" s="73">
+      <c r="H16" s="60">
         <f>AVERAGE(H5,H8,H11)</f>
         <v>0.90476190476190477</v>
       </c>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="11" t="s">
+      <c r="A19" s="66" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="11"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
+      <c r="B19" s="66"/>
+      <c r="C19" s="66"/>
+      <c r="D19" s="66"/>
+      <c r="E19" s="66"/>
+      <c r="F19" s="66"/>
+      <c r="G19" s="66"/>
+      <c r="H19" s="66"/>
+      <c r="I19" s="66"/>
+      <c r="J19" s="66"/>
+      <c r="K19" s="66"/>
     </row>
     <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="50"/>
-      <c r="B20" s="50" t="s">
+      <c r="A20" s="37"/>
+      <c r="B20" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="76" t="s">
+      <c r="C20" s="63" t="s">
         <v>6</v>
       </c>
-      <c r="D20" s="50" t="s">
+      <c r="D20" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="E20" s="50" t="s">
+      <c r="E20" s="37" t="s">
         <v>59</v>
       </c>
-      <c r="F20" s="50" t="s">
+      <c r="F20" s="37" t="s">
         <v>60</v>
       </c>
-      <c r="G20" s="50" t="s">
+      <c r="G20" s="37" t="s">
         <v>61</v>
       </c>
-      <c r="H20" s="50" t="s">
+      <c r="H20" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="I20" s="50" t="s">
+      <c r="I20" s="37" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="58"/>
-      <c r="B21" s="59" t="s">
+      <c r="A21" s="45"/>
+      <c r="B21" s="46" t="s">
         <v>64</v>
       </c>
-      <c r="C21" s="58" t="s">
+      <c r="C21" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="D21" s="69">
+      <c r="D21" s="56">
         <f>SUMPRODUCT(([1]Rådata!D6:G6="J")*1)</f>
         <v>4</v>
       </c>
-      <c r="E21" s="69">
+      <c r="E21" s="56">
         <f>SUMPRODUCT(([1]Rådata!H6:K6="J")*1)</f>
         <v>4</v>
       </c>
-      <c r="F21" s="69">
+      <c r="F21" s="56">
         <f>SUMPRODUCT(([1]Rådata!D19:G19="J")*1)</f>
         <v>0</v>
       </c>
-      <c r="G21" s="69">
+      <c r="G21" s="56">
         <f>SUMPRODUCT(([1]Rådata!H19:K19="J")*1)</f>
         <v>4</v>
       </c>
-      <c r="H21" s="69">
+      <c r="H21" s="56">
         <f>SUMPRODUCT(([1]Rådata!D32:G32="J")*1)</f>
         <v>1</v>
       </c>
-      <c r="I21" s="69">
+      <c r="I21" s="56">
         <f>SUMPRODUCT(([1]Rådata!H32:K32="J")*1)</f>
         <v>4</v>
       </c>
     </row>
     <row r="22" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="48"/>
-      <c r="B22" s="60" t="s">
+      <c r="A22" s="35"/>
+      <c r="B22" s="47" t="s">
         <v>65</v>
       </c>
-      <c r="C22" s="48" t="s">
+      <c r="C22" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="69">
+      <c r="D22" s="56">
         <f>SUMPRODUCT(([1]Rådata!D7:G7="J")*1)</f>
         <v>3</v>
       </c>
-      <c r="E22" s="69">
+      <c r="E22" s="56">
         <f>SUMPRODUCT(([1]Rådata!H7:K7="J")*1)</f>
         <v>4</v>
       </c>
-      <c r="F22" s="69">
+      <c r="F22" s="56">
         <f>SUMPRODUCT(([1]Rådata!D20:G20="J")*1)</f>
         <v>4</v>
       </c>
-      <c r="G22" s="69">
+      <c r="G22" s="56">
         <f>SUMPRODUCT(([1]Rådata!H20:K20="J")*1)</f>
         <v>4</v>
       </c>
-      <c r="H22" s="69">
+      <c r="H22" s="56">
         <f>SUMPRODUCT(([1]Rådata!D33:G33="J")*1)</f>
         <v>3</v>
       </c>
-      <c r="I22" s="69">
+      <c r="I22" s="56">
         <f>SUMPRODUCT(([1]Rådata!H33:K33="J")*1)</f>
         <v>4</v>
       </c>
     </row>
     <row r="23" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="58"/>
-      <c r="B23" s="61" t="s">
+      <c r="A23" s="45"/>
+      <c r="B23" s="48" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="58" t="s">
+      <c r="C23" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="D23" s="69">
+      <c r="D23" s="56">
         <f>SUMPRODUCT(([1]Rådata!D8:G8="J")*1)</f>
         <v>0</v>
       </c>
-      <c r="E23" s="69">
+      <c r="E23" s="56">
         <f>SUMPRODUCT(([1]Rådata!H8:K8="J")*1)</f>
         <v>3</v>
       </c>
-      <c r="F23" s="69">
+      <c r="F23" s="56">
         <f>SUMPRODUCT(([1]Rådata!D21:G21="J")*1)</f>
         <v>0</v>
       </c>
-      <c r="G23" s="69">
+      <c r="G23" s="56">
         <f>SUMPRODUCT(([1]Rådata!H21:K21="J")*1)</f>
         <v>4</v>
       </c>
-      <c r="H23" s="69">
+      <c r="H23" s="56">
         <f>SUMPRODUCT(([1]Rådata!D34:G34="J")*1)</f>
         <v>0</v>
       </c>
-      <c r="I23" s="69">
+      <c r="I23" s="56">
         <f>SUMPRODUCT(([1]Rådata!H34:K34="J")*1)</f>
         <v>2</v>
       </c>
     </row>
     <row r="24" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="48"/>
-      <c r="B24" s="62" t="s">
+      <c r="A24" s="35"/>
+      <c r="B24" s="49" t="s">
         <v>67</v>
       </c>
-      <c r="C24" s="48" t="s">
+      <c r="C24" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="D24" s="69">
+      <c r="D24" s="56">
         <f>SUMPRODUCT(([1]Rådata!D9:G9="J")*1)</f>
         <v>0</v>
       </c>
-      <c r="E24" s="69">
+      <c r="E24" s="56">
         <f>SUMPRODUCT(([1]Rådata!H9:K9="J")*1)</f>
         <v>3</v>
       </c>
-      <c r="F24" s="69">
+      <c r="F24" s="56">
         <f>SUMPRODUCT(([1]Rådata!D22:G22="J")*1)</f>
         <v>1</v>
       </c>
-      <c r="G24" s="69">
+      <c r="G24" s="56">
         <f>SUMPRODUCT(([1]Rådata!H22:K22="J")*1)</f>
         <v>4</v>
       </c>
-      <c r="H24" s="69">
+      <c r="H24" s="56">
         <f>SUMPRODUCT(([1]Rådata!D35:G35="J")*1)</f>
         <v>0</v>
       </c>
-      <c r="I24" s="69">
+      <c r="I24" s="56">
         <f>SUMPRODUCT(([1]Rådata!H35:K35="J")*1)</f>
         <v>4</v>
       </c>
     </row>
     <row r="25" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="58"/>
-      <c r="B25" s="61" t="s">
+      <c r="A25" s="45"/>
+      <c r="B25" s="48" t="s">
         <v>68</v>
       </c>
-      <c r="C25" s="58" t="s">
+      <c r="C25" s="45" t="s">
         <v>26</v>
       </c>
-      <c r="D25" s="69">
+      <c r="D25" s="56">
         <f>SUMPRODUCT(([1]Rådata!D10:G10="J")*1)</f>
         <v>2</v>
       </c>
-      <c r="E25" s="69">
+      <c r="E25" s="56">
         <f>SUMPRODUCT(([1]Rådata!H10:K10="J")*1)</f>
         <v>3</v>
       </c>
-      <c r="F25" s="69">
+      <c r="F25" s="56">
         <f>SUMPRODUCT(([1]Rådata!D23:G23="J")*1)</f>
         <v>0</v>
       </c>
-      <c r="G25" s="69">
+      <c r="G25" s="56">
         <f>SUMPRODUCT(([1]Rådata!H23:K23="J")*1)</f>
         <v>4</v>
       </c>
-      <c r="H25" s="69">
+      <c r="H25" s="56">
         <f>SUMPRODUCT(([1]Rådata!D36:G36="J")*1)</f>
         <v>0</v>
       </c>
-      <c r="I25" s="69">
+      <c r="I25" s="56">
         <f>SUMPRODUCT(([1]Rådata!H36:K36="J")*1)</f>
         <v>4</v>
       </c>
     </row>
     <row r="26" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="48"/>
-      <c r="B26" s="62" t="s">
+      <c r="A26" s="35"/>
+      <c r="B26" s="49" t="s">
         <v>69</v>
       </c>
-      <c r="C26" s="48" t="s">
+      <c r="C26" s="35" t="s">
         <v>28</v>
       </c>
-      <c r="D26" s="69">
+      <c r="D26" s="56">
         <f>SUMPRODUCT(([1]Rådata!D11:G11="J")*1)</f>
         <v>0</v>
       </c>
-      <c r="E26" s="69">
+      <c r="E26" s="56">
         <f>SUMPRODUCT(([1]Rådata!H11:K11="J")*1)</f>
         <v>2</v>
       </c>
-      <c r="F26" s="69">
+      <c r="F26" s="56">
         <f>SUMPRODUCT(([1]Rådata!D24:G24="J")*1)</f>
         <v>2</v>
       </c>
-      <c r="G26" s="69">
+      <c r="G26" s="56">
         <f>SUMPRODUCT(([1]Rådata!H24:K24="J")*1)</f>
         <v>4</v>
       </c>
-      <c r="H26" s="69">
+      <c r="H26" s="56">
         <f>SUMPRODUCT(([1]Rådata!D37:G37="J")*1)</f>
         <v>0</v>
       </c>
-      <c r="I26" s="69">
+      <c r="I26" s="56">
         <f>SUMPRODUCT(([1]Rådata!H37:K37="J")*1)</f>
         <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="58"/>
-      <c r="B27" s="61" t="s">
+      <c r="A27" s="45"/>
+      <c r="B27" s="48" t="s">
         <v>70</v>
       </c>
-      <c r="C27" s="58" t="s">
+      <c r="C27" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="69">
+      <c r="D27" s="56">
         <f>SUMPRODUCT(([1]Rådata!D12:G12="J")*1)</f>
         <v>4</v>
       </c>
-      <c r="E27" s="69">
+      <c r="E27" s="56">
         <f>SUMPRODUCT(([1]Rådata!H12:K12="J")*1)</f>
         <v>4</v>
       </c>
-      <c r="F27" s="69">
+      <c r="F27" s="56">
         <f>SUMPRODUCT(([1]Rådata!D25:G25="J")*1)</f>
         <v>4</v>
       </c>
-      <c r="G27" s="69">
+      <c r="G27" s="56">
         <f>SUMPRODUCT(([1]Rådata!H25:K25="J")*1)</f>
         <v>4</v>
       </c>
-      <c r="H27" s="69">
+      <c r="H27" s="56">
         <f>SUMPRODUCT(([1]Rådata!D38:G38="J")*1)</f>
         <v>3</v>
       </c>
-      <c r="I27" s="69">
+      <c r="I27" s="56">
         <f>SUMPRODUCT(([1]Rådata!H38:K38="J")*1)</f>
         <v>4</v>
       </c>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="74" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="3"/>
-      <c r="C30" s="3"/>
-      <c r="D30" s="3"/>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
+      <c r="B30" s="74"/>
+      <c r="C30" s="74"/>
+      <c r="D30" s="74"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="74"/>
+      <c r="I30" s="74"/>
+      <c r="J30" s="74"/>
+      <c r="K30" s="74"/>
     </row>
     <row r="31" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="63"/>
-      <c r="B31" s="2" t="s">
+      <c r="A31" s="50"/>
+      <c r="B31" s="75" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="2"/>
-      <c r="D31" s="2"/>
-      <c r="E31" s="2"/>
-      <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-      <c r="I31" s="2"/>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2"/>
+      <c r="C31" s="75"/>
+      <c r="D31" s="75"/>
+      <c r="E31" s="75"/>
+      <c r="F31" s="75"/>
+      <c r="G31" s="75"/>
+      <c r="H31" s="75"/>
+      <c r="I31" s="75"/>
+      <c r="J31" s="75"/>
+      <c r="K31" s="75"/>
     </row>
     <row r="32" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="63"/>
-      <c r="B32" s="2" t="s">
+      <c r="A32" s="50"/>
+      <c r="B32" s="75" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="2"/>
-      <c r="D32" s="2"/>
-      <c r="E32" s="2"/>
-      <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-      <c r="I32" s="2"/>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2"/>
+      <c r="C32" s="75"/>
+      <c r="D32" s="75"/>
+      <c r="E32" s="75"/>
+      <c r="F32" s="75"/>
+      <c r="G32" s="75"/>
+      <c r="H32" s="75"/>
+      <c r="I32" s="75"/>
+      <c r="J32" s="75"/>
+      <c r="K32" s="75"/>
     </row>
     <row r="33" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="63"/>
-      <c r="B33" s="2" t="s">
+      <c r="A33" s="50"/>
+      <c r="B33" s="75" t="s">
         <v>74</v>
       </c>
-      <c r="C33" s="2"/>
-      <c r="D33" s="2"/>
-      <c r="E33" s="2"/>
-      <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-      <c r="I33" s="2"/>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2"/>
+      <c r="C33" s="75"/>
+      <c r="D33" s="75"/>
+      <c r="E33" s="75"/>
+      <c r="F33" s="75"/>
+      <c r="G33" s="75"/>
+      <c r="H33" s="75"/>
+      <c r="I33" s="75"/>
+      <c r="J33" s="75"/>
+      <c r="K33" s="75"/>
     </row>
     <row r="34" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="63"/>
-      <c r="B34" s="2" t="s">
+      <c r="A34" s="50"/>
+      <c r="B34" s="75" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="2"/>
-      <c r="D34" s="2"/>
-      <c r="E34" s="2"/>
-      <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-      <c r="I34" s="2"/>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2"/>
+      <c r="C34" s="75"/>
+      <c r="D34" s="75"/>
+      <c r="E34" s="75"/>
+      <c r="F34" s="75"/>
+      <c r="G34" s="75"/>
+      <c r="H34" s="75"/>
+      <c r="I34" s="75"/>
+      <c r="J34" s="75"/>
+      <c r="K34" s="75"/>
     </row>
     <row r="35" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="64"/>
-      <c r="B35" s="1" t="s">
+      <c r="A35" s="51"/>
+      <c r="B35" s="76" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
+      <c r="C35" s="76"/>
+      <c r="D35" s="76"/>
+      <c r="E35" s="76"/>
+      <c r="F35" s="76"/>
+      <c r="G35" s="76"/>
+      <c r="H35" s="76"/>
+      <c r="I35" s="76"/>
+      <c r="J35" s="76"/>
+      <c r="K35" s="76"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3836,6 +3838,18 @@
     <mergeCell ref="A19:K19"/>
     <mergeCell ref="A30:K30"/>
   </mergeCells>
+  <conditionalFormatting sqref="D4:G5 D7:G8 D10:G11">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FFF8696B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FF63BE7B"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D21:I27">
     <cfRule type="colorScale" priority="5">
       <colorScale>
@@ -3880,18 +3894,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D4:G5 D7:G8 D10:G11">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FFF8696B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FF63BE7B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
@@ -3907,73 +3909,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="52" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="2" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="66"/>
+      <c r="B2" s="53"/>
     </row>
     <row r="3" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="67" t="s">
+      <c r="B3" s="54" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="4" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="66" t="s">
+      <c r="B4" s="53" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="5" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="66" t="s">
+      <c r="B5" s="53" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="6" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="66" t="s">
+      <c r="B6" s="53" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="7" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="66"/>
+      <c r="B7" s="53"/>
     </row>
     <row r="8" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="68" t="s">
+      <c r="B8" s="55" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="66" t="s">
+      <c r="B9" s="53" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="10" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="66" t="s">
+      <c r="B10" s="53" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="11" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="66" t="s">
+      <c r="B11" s="53" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="12" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="66" t="s">
+      <c r="B12" s="53" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="13" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="53" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="14" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="66" t="s">
+      <c r="B14" s="53" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="15" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="66" t="s">
+      <c r="B15" s="53" t="s">
         <v>89</v>
       </c>
     </row>

--- a/data/Delstidue 1/Resultater_DS1_Origami.xlsx
+++ b/data/Delstidue 1/Resultater_DS1_Origami.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ramboll-my.sharepoint.com/personal/ahmad_rezaie_ramboll_no/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="54" documentId="8_{C64A8CAB-14C6-401B-A689-679E1038BF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EACB3A07-DF3E-4464-B567-6EE1ACA246AA}"/>
+  <xr:revisionPtr revIDLastSave="55" documentId="8_{C64A8CAB-14C6-401B-A689-679E1038BF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A6303CA-46AC-419C-980B-1F60F0FED253}"/>
   <bookViews>
-    <workbookView xWindow="31710" yWindow="-375" windowWidth="21600" windowHeight="11295" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-1965" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rådata" sheetId="1" r:id="rId1"/>
@@ -854,37 +854,28 @@
     <xf numFmtId="0" fontId="19" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -892,6 +883,15 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1741,19 +1741,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="68" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="68"/>
+      <c r="K1" s="68"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
@@ -1771,10 +1771,10 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="69" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="65"/>
+      <c r="B2" s="69"/>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
@@ -1791,18 +1791,18 @@
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="66" t="s">
+      <c r="D3" s="70" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="67" t="s">
+      <c r="E3" s="70"/>
+      <c r="F3" s="70"/>
+      <c r="G3" s="70"/>
+      <c r="H3" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
+      <c r="I3" s="71"/>
+      <c r="J3" s="71"/>
+      <c r="K3" s="71"/>
     </row>
     <row r="4" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
@@ -1840,19 +1840,19 @@
       </c>
     </row>
     <row r="5" spans="1:26" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
+      <c r="B5" s="67"/>
+      <c r="C5" s="67"/>
+      <c r="D5" s="67"/>
+      <c r="E5" s="67"/>
+      <c r="F5" s="67"/>
+      <c r="G5" s="67"/>
+      <c r="H5" s="67"/>
+      <c r="I5" s="67"/>
+      <c r="J5" s="67"/>
+      <c r="K5" s="67"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
@@ -2100,11 +2100,11 @@
       </c>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="69" t="s">
+      <c r="A13" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="69"/>
-      <c r="C13" s="69"/>
+      <c r="B13" s="64"/>
+      <c r="C13" s="64"/>
       <c r="D13" s="26">
         <f t="shared" ref="D13:K13" si="0">COUNTIF(D6:D12,"J")</f>
         <v>4</v>
@@ -2139,11 +2139,11 @@
       </c>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="70" t="s">
+      <c r="A14" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="70"/>
-      <c r="C14" s="70"/>
+      <c r="B14" s="65"/>
+      <c r="C14" s="65"/>
       <c r="D14" s="28">
         <f t="shared" ref="D14:K14" si="1">COUNTIF(D6:D12,"N")</f>
         <v>3</v>
@@ -2178,11 +2178,11 @@
       </c>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="71" t="s">
+      <c r="A15" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="71"/>
+      <c r="B15" s="66"/>
+      <c r="C15" s="66"/>
       <c r="D15" s="30">
         <v>7</v>
       </c>
@@ -2209,11 +2209,11 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="71" t="s">
+      <c r="A16" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="71"/>
+      <c r="B16" s="66"/>
+      <c r="C16" s="66"/>
       <c r="D16" s="32">
         <f t="shared" ref="D16:K16" si="2">IFERROR(D13/D15,0)</f>
         <v>0.5714285714285714</v>
@@ -2248,19 +2248,19 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="68" t="s">
+      <c r="A18" s="67" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="68"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="68"/>
-      <c r="H18" s="68"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="68"/>
-      <c r="K18" s="68"/>
+      <c r="B18" s="67"/>
+      <c r="C18" s="67"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="67"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="67"/>
+      <c r="H18" s="67"/>
+      <c r="I18" s="67"/>
+      <c r="J18" s="67"/>
+      <c r="K18" s="67"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
@@ -2508,11 +2508,11 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="69" t="s">
+      <c r="A26" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="69"/>
-      <c r="C26" s="69"/>
+      <c r="B26" s="64"/>
+      <c r="C26" s="64"/>
       <c r="D26" s="26">
         <f t="shared" ref="D26:K26" si="3">COUNTIF(D19:D25,"J")</f>
         <v>3</v>
@@ -2547,11 +2547,11 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="70" t="s">
+      <c r="A27" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="70"/>
-      <c r="C27" s="70"/>
+      <c r="B27" s="65"/>
+      <c r="C27" s="65"/>
       <c r="D27" s="28">
         <f t="shared" ref="D27:K27" si="4">COUNTIF(D19:D25,"N")</f>
         <v>4</v>
@@ -2586,11 +2586,11 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="71" t="s">
+      <c r="A28" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="71"/>
-      <c r="C28" s="71"/>
+      <c r="B28" s="66"/>
+      <c r="C28" s="66"/>
       <c r="D28" s="30" t="s">
         <v>30</v>
       </c>
@@ -2617,11 +2617,11 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="71" t="s">
+      <c r="A29" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="71"/>
-      <c r="C29" s="71"/>
+      <c r="B29" s="66"/>
+      <c r="C29" s="66"/>
       <c r="D29" s="32">
         <f t="shared" ref="D29:K29" si="5">IFERROR(D26/D28,0)</f>
         <v>0.42857142857142855</v>
@@ -2656,19 +2656,19 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="68" t="s">
+      <c r="A31" s="67" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="68"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="68"/>
-      <c r="H31" s="68"/>
-      <c r="I31" s="68"/>
-      <c r="J31" s="68"/>
-      <c r="K31" s="68"/>
+      <c r="B31" s="67"/>
+      <c r="C31" s="67"/>
+      <c r="D31" s="67"/>
+      <c r="E31" s="67"/>
+      <c r="F31" s="67"/>
+      <c r="G31" s="67"/>
+      <c r="H31" s="67"/>
+      <c r="I31" s="67"/>
+      <c r="J31" s="67"/>
+      <c r="K31" s="67"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
@@ -2891,7 +2891,7 @@
         <v>31</v>
       </c>
       <c r="D38" s="25" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="E38" s="23" t="s">
         <v>16</v>
@@ -2916,16 +2916,16 @@
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="69" t="s">
+      <c r="A39" s="64" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="69"/>
-      <c r="C39" s="69"/>
+      <c r="B39" s="64"/>
+      <c r="C39" s="64"/>
       <c r="D39" s="26">
         <v>1</v>
       </c>
       <c r="E39" s="27">
-        <f t="shared" ref="D39:K39" si="6">COUNTIF(E32:E38,"J")</f>
+        <f t="shared" ref="E39:K39" si="6">COUNTIF(E32:E38,"J")</f>
         <v>2</v>
       </c>
       <c r="F39" s="27">
@@ -2954,16 +2954,16 @@
       </c>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="70" t="s">
+      <c r="A40" s="65" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="70"/>
-      <c r="C40" s="70"/>
+      <c r="B40" s="65"/>
+      <c r="C40" s="65"/>
       <c r="D40" s="28">
         <v>6</v>
       </c>
       <c r="E40" s="29">
-        <f t="shared" ref="D40:K40" si="7">COUNTIF(E32:E38,"N")</f>
+        <f t="shared" ref="E40:K40" si="7">COUNTIF(E32:E38,"N")</f>
         <v>5</v>
       </c>
       <c r="F40" s="29">
@@ -2992,11 +2992,11 @@
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="71" t="s">
+      <c r="A41" s="66" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="71"/>
-      <c r="C41" s="71"/>
+      <c r="B41" s="66"/>
+      <c r="C41" s="66"/>
       <c r="D41" s="30" t="s">
         <v>30</v>
       </c>
@@ -3023,11 +3023,11 @@
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="71" t="s">
+      <c r="A42" s="66" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
+      <c r="B42" s="66"/>
+      <c r="C42" s="66"/>
       <c r="D42" s="32">
         <f t="shared" ref="D42:K42" si="8">IFERROR(D39/D41,0)</f>
         <v>0.14285714285714285</v>
@@ -3063,6 +3063,16 @@
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D3:G3"/>
+    <mergeCell ref="H3:K3"/>
+    <mergeCell ref="A5:K5"/>
+    <mergeCell ref="A13:C13"/>
+    <mergeCell ref="A14:C14"/>
+    <mergeCell ref="A15:C15"/>
+    <mergeCell ref="A16:C16"/>
+    <mergeCell ref="A18:K18"/>
     <mergeCell ref="A39:C39"/>
     <mergeCell ref="A40:C40"/>
     <mergeCell ref="A41:C41"/>
@@ -3072,16 +3082,6 @@
     <mergeCell ref="A28:C28"/>
     <mergeCell ref="A29:C29"/>
     <mergeCell ref="A31:K31"/>
-    <mergeCell ref="A13:C13"/>
-    <mergeCell ref="A14:C14"/>
-    <mergeCell ref="A15:C15"/>
-    <mergeCell ref="A16:C16"/>
-    <mergeCell ref="A18:K18"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D3:G3"/>
-    <mergeCell ref="H3:K3"/>
-    <mergeCell ref="A5:K5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.51180555555555596"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3105,34 +3105,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="74" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
+      <c r="B1" s="74"/>
+      <c r="C1" s="74"/>
+      <c r="D1" s="74"/>
+      <c r="E1" s="74"/>
+      <c r="F1" s="74"/>
+      <c r="G1" s="74"/>
+      <c r="H1" s="74"/>
+      <c r="I1" s="74"/>
+      <c r="J1" s="74"/>
+      <c r="K1" s="74"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="70" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
+      <c r="B2" s="70"/>
+      <c r="C2" s="70"/>
+      <c r="D2" s="70"/>
+      <c r="E2" s="70"/>
+      <c r="F2" s="70"/>
+      <c r="G2" s="70"/>
+      <c r="H2" s="70"/>
+      <c r="I2" s="70"/>
+      <c r="J2" s="70"/>
+      <c r="K2" s="70"/>
     </row>
     <row r="3" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A3" s="37"/>
@@ -3426,15 +3426,15 @@
       <c r="H13" s="58"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="73" t="s">
+      <c r="A14" s="75" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="73"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="75"/>
+      <c r="F14" s="75"/>
+      <c r="G14" s="75"/>
       <c r="H14" s="59"/>
       <c r="I14" s="44"/>
       <c r="J14" s="44"/>
@@ -3463,19 +3463,19 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="66" t="s">
+      <c r="A19" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="66"/>
+      <c r="B19" s="70"/>
+      <c r="C19" s="70"/>
+      <c r="D19" s="70"/>
+      <c r="E19" s="70"/>
+      <c r="F19" s="70"/>
+      <c r="G19" s="70"/>
+      <c r="H19" s="70"/>
+      <c r="I19" s="70"/>
+      <c r="J19" s="70"/>
+      <c r="K19" s="70"/>
     </row>
     <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="37"/>
@@ -3736,107 +3736,107 @@
       </c>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="74" t="s">
+      <c r="A30" s="76" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="74"/>
-      <c r="C30" s="74"/>
-      <c r="D30" s="74"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-      <c r="I30" s="74"/>
-      <c r="J30" s="74"/>
-      <c r="K30" s="74"/>
+      <c r="B30" s="76"/>
+      <c r="C30" s="76"/>
+      <c r="D30" s="76"/>
+      <c r="E30" s="76"/>
+      <c r="F30" s="76"/>
+      <c r="G30" s="76"/>
+      <c r="H30" s="76"/>
+      <c r="I30" s="76"/>
+      <c r="J30" s="76"/>
+      <c r="K30" s="76"/>
     </row>
     <row r="31" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="50"/>
-      <c r="B31" s="75" t="s">
+      <c r="B31" s="72" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="75"/>
-      <c r="D31" s="75"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="75"/>
-      <c r="K31" s="75"/>
+      <c r="C31" s="72"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="72"/>
+      <c r="F31" s="72"/>
+      <c r="G31" s="72"/>
+      <c r="H31" s="72"/>
+      <c r="I31" s="72"/>
+      <c r="J31" s="72"/>
+      <c r="K31" s="72"/>
     </row>
     <row r="32" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="50"/>
-      <c r="B32" s="75" t="s">
+      <c r="B32" s="72" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="75"/>
-      <c r="D32" s="75"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
-      <c r="K32" s="75"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="72"/>
+      <c r="F32" s="72"/>
+      <c r="G32" s="72"/>
+      <c r="H32" s="72"/>
+      <c r="I32" s="72"/>
+      <c r="J32" s="72"/>
+      <c r="K32" s="72"/>
     </row>
     <row r="33" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="50"/>
-      <c r="B33" s="75" t="s">
+      <c r="B33" s="72" t="s">
         <v>74</v>
       </c>
-      <c r="C33" s="75"/>
-      <c r="D33" s="75"/>
-      <c r="E33" s="75"/>
-      <c r="F33" s="75"/>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75"/>
-      <c r="K33" s="75"/>
+      <c r="C33" s="72"/>
+      <c r="D33" s="72"/>
+      <c r="E33" s="72"/>
+      <c r="F33" s="72"/>
+      <c r="G33" s="72"/>
+      <c r="H33" s="72"/>
+      <c r="I33" s="72"/>
+      <c r="J33" s="72"/>
+      <c r="K33" s="72"/>
     </row>
     <row r="34" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="50"/>
-      <c r="B34" s="75" t="s">
+      <c r="B34" s="72" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="75"/>
-      <c r="D34" s="75"/>
-      <c r="E34" s="75"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="75"/>
-      <c r="J34" s="75"/>
-      <c r="K34" s="75"/>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="72"/>
+      <c r="F34" s="72"/>
+      <c r="G34" s="72"/>
+      <c r="H34" s="72"/>
+      <c r="I34" s="72"/>
+      <c r="J34" s="72"/>
+      <c r="K34" s="72"/>
     </row>
     <row r="35" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="51"/>
-      <c r="B35" s="76" t="s">
+      <c r="B35" s="73" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="76"/>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
-      <c r="I35" s="76"/>
-      <c r="J35" s="76"/>
-      <c r="K35" s="76"/>
+      <c r="C35" s="73"/>
+      <c r="D35" s="73"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73"/>
+      <c r="J35" s="73"/>
+      <c r="K35" s="73"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A19:K19"/>
+    <mergeCell ref="A30:K30"/>
     <mergeCell ref="B31:K31"/>
     <mergeCell ref="B32:K32"/>
     <mergeCell ref="B33:K33"/>
     <mergeCell ref="B34:K34"/>
     <mergeCell ref="B35:K35"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A19:K19"/>
-    <mergeCell ref="A30:K30"/>
   </mergeCells>
   <conditionalFormatting sqref="D4:G5 D7:G8 D10:G11">
     <cfRule type="colorScale" priority="1">

--- a/data/Delstidue 1/Resultater_DS1_Origami.xlsx
+++ b/data/Delstidue 1/Resultater_DS1_Origami.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ramboll-my.sharepoint.com/personal/ahmad_rezaie_ramboll_no/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="8_{C64A8CAB-14C6-401B-A689-679E1038BF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A6303CA-46AC-419C-980B-1F60F0FED253}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="8_{C64A8CAB-14C6-401B-A689-679E1038BF6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CF360A84-3286-44A6-ABB0-22FA882FF5E2}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-1965" windowWidth="29040" windowHeight="17520" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28920" yWindow="-1830" windowWidth="15330" windowHeight="10770" tabRatio="500" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Rådata" sheetId="1" r:id="rId1"/>
@@ -295,9 +295,6 @@
     <t>5. Gå til fanen «Analyse og resultater» for å se gjennomsnittlig Precision per case, modell og samlet</t>
   </si>
   <si>
-    <t>Feltstruktur per case (13 felt totalt, 12 evaluerbare):</t>
-  </si>
-  <si>
     <t>§11-2: Risikoklasse (prompt 1)</t>
   </si>
   <si>
@@ -317,6 +314,9 @@
   </si>
   <si>
     <t>§11-4: Utvendig trappeløp, beskyttet mot flammepåvirkning og strålevarme (prompt 7)</t>
+  </si>
+  <si>
+    <t>Feltstruktur per case (7):</t>
   </si>
 </sst>
 </file>
@@ -854,13 +854,28 @@
     <xf numFmtId="0" fontId="19" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -876,21 +891,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1741,19 +1741,19 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="64" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="64"/>
-      <c r="C1" s="64"/>
-      <c r="D1" s="64"/>
-      <c r="E1" s="64"/>
-      <c r="F1" s="64"/>
-      <c r="G1" s="64"/>
-      <c r="H1" s="64"/>
-      <c r="I1" s="64"/>
-      <c r="J1" s="64"/>
-      <c r="K1" s="64"/>
+      <c r="B1" s="70"/>
+      <c r="C1" s="70"/>
+      <c r="D1" s="70"/>
+      <c r="E1" s="70"/>
+      <c r="F1" s="70"/>
+      <c r="G1" s="70"/>
+      <c r="H1" s="70"/>
+      <c r="I1" s="70"/>
+      <c r="J1" s="70"/>
+      <c r="K1" s="70"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
       <c r="N1" s="2"/>
@@ -1771,10 +1771,10 @@
       <c r="Z1" s="2"/>
     </row>
     <row r="2" spans="1:26" ht="21.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="65" t="s">
+      <c r="A2" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="65"/>
+      <c r="B2" s="71"/>
       <c r="C2" s="3" t="s">
         <v>2</v>
       </c>
@@ -1791,18 +1791,18 @@
       <c r="A3" s="5"/>
       <c r="B3" s="5"/>
       <c r="C3" s="6"/>
-      <c r="D3" s="66" t="s">
+      <c r="D3" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="66"/>
-      <c r="F3" s="66"/>
-      <c r="G3" s="66"/>
-      <c r="H3" s="67" t="s">
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="72" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="67"/>
-      <c r="J3" s="67"/>
-      <c r="K3" s="67"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="72"/>
+      <c r="K3" s="72"/>
     </row>
     <row r="4" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
@@ -1840,19 +1840,19 @@
       </c>
     </row>
     <row r="5" spans="1:26" s="12" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="73" t="s">
         <v>12</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
+      <c r="B5" s="73"/>
+      <c r="C5" s="73"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="73"/>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+      <c r="J5" s="73"/>
+      <c r="K5" s="73"/>
     </row>
     <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
@@ -2100,11 +2100,11 @@
       </c>
     </row>
     <row r="13" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="69" t="s">
+      <c r="A13" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="B13" s="69"/>
-      <c r="C13" s="69"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="74"/>
       <c r="D13" s="26">
         <f t="shared" ref="D13:K13" si="0">COUNTIF(D6:D12,"J")</f>
         <v>4</v>
@@ -2139,11 +2139,11 @@
       </c>
     </row>
     <row r="14" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="70" t="s">
+      <c r="A14" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="B14" s="70"/>
-      <c r="C14" s="70"/>
+      <c r="B14" s="75"/>
+      <c r="C14" s="75"/>
       <c r="D14" s="28">
         <f t="shared" ref="D14:K14" si="1">COUNTIF(D6:D12,"N")</f>
         <v>3</v>
@@ -2178,11 +2178,11 @@
       </c>
     </row>
     <row r="15" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="71" t="s">
+      <c r="A15" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="B15" s="71"/>
-      <c r="C15" s="71"/>
+      <c r="B15" s="76"/>
+      <c r="C15" s="76"/>
       <c r="D15" s="30">
         <v>7</v>
       </c>
@@ -2209,11 +2209,11 @@
       </c>
     </row>
     <row r="16" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="71" t="s">
+      <c r="A16" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="B16" s="71"/>
-      <c r="C16" s="71"/>
+      <c r="B16" s="76"/>
+      <c r="C16" s="76"/>
       <c r="D16" s="32">
         <f t="shared" ref="D16:K16" si="2">IFERROR(D13/D15,0)</f>
         <v>0.5714285714285714</v>
@@ -2248,19 +2248,19 @@
       </c>
     </row>
     <row r="18" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="68" t="s">
+      <c r="A18" s="73" t="s">
         <v>36</v>
       </c>
-      <c r="B18" s="68"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="68"/>
-      <c r="H18" s="68"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="68"/>
-      <c r="K18" s="68"/>
+      <c r="B18" s="73"/>
+      <c r="C18" s="73"/>
+      <c r="D18" s="73"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73"/>
+      <c r="J18" s="73"/>
+      <c r="K18" s="73"/>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="34" t="s">
@@ -2508,11 +2508,11 @@
       </c>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="69" t="s">
+      <c r="A26" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="B26" s="69"/>
-      <c r="C26" s="69"/>
+      <c r="B26" s="74"/>
+      <c r="C26" s="74"/>
       <c r="D26" s="26">
         <f t="shared" ref="D26:K26" si="3">COUNTIF(D19:D25,"J")</f>
         <v>3</v>
@@ -2547,11 +2547,11 @@
       </c>
     </row>
     <row r="27" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="70" t="s">
+      <c r="A27" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="B27" s="70"/>
-      <c r="C27" s="70"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="75"/>
       <c r="D27" s="28">
         <f t="shared" ref="D27:K27" si="4">COUNTIF(D19:D25,"N")</f>
         <v>4</v>
@@ -2586,11 +2586,11 @@
       </c>
     </row>
     <row r="28" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="71" t="s">
+      <c r="A28" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="B28" s="71"/>
-      <c r="C28" s="71"/>
+      <c r="B28" s="76"/>
+      <c r="C28" s="76"/>
       <c r="D28" s="30" t="s">
         <v>30</v>
       </c>
@@ -2617,11 +2617,11 @@
       </c>
     </row>
     <row r="29" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="71" t="s">
+      <c r="A29" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="B29" s="71"/>
-      <c r="C29" s="71"/>
+      <c r="B29" s="76"/>
+      <c r="C29" s="76"/>
       <c r="D29" s="32">
         <f t="shared" ref="D29:K29" si="5">IFERROR(D26/D28,0)</f>
         <v>0.42857142857142855</v>
@@ -2656,19 +2656,19 @@
       </c>
     </row>
     <row r="31" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="68" t="s">
+      <c r="A31" s="73" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="68"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="68"/>
-      <c r="H31" s="68"/>
-      <c r="I31" s="68"/>
-      <c r="J31" s="68"/>
-      <c r="K31" s="68"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="73"/>
+      <c r="D31" s="73"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73"/>
+      <c r="J31" s="73"/>
+      <c r="K31" s="73"/>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="19" t="s">
@@ -2916,11 +2916,11 @@
       </c>
     </row>
     <row r="39" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="69" t="s">
+      <c r="A39" s="74" t="s">
         <v>32</v>
       </c>
-      <c r="B39" s="69"/>
-      <c r="C39" s="69"/>
+      <c r="B39" s="74"/>
+      <c r="C39" s="74"/>
       <c r="D39" s="26">
         <v>1</v>
       </c>
@@ -2954,11 +2954,11 @@
       </c>
     </row>
     <row r="40" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="70" t="s">
+      <c r="A40" s="75" t="s">
         <v>33</v>
       </c>
-      <c r="B40" s="70"/>
-      <c r="C40" s="70"/>
+      <c r="B40" s="75"/>
+      <c r="C40" s="75"/>
       <c r="D40" s="28">
         <v>6</v>
       </c>
@@ -2992,11 +2992,11 @@
       </c>
     </row>
     <row r="41" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="71" t="s">
+      <c r="A41" s="76" t="s">
         <v>34</v>
       </c>
-      <c r="B41" s="71"/>
-      <c r="C41" s="71"/>
+      <c r="B41" s="76"/>
+      <c r="C41" s="76"/>
       <c r="D41" s="30" t="s">
         <v>30</v>
       </c>
@@ -3023,11 +3023,11 @@
       </c>
     </row>
     <row r="42" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="71" t="s">
+      <c r="A42" s="76" t="s">
         <v>35</v>
       </c>
-      <c r="B42" s="71"/>
-      <c r="C42" s="71"/>
+      <c r="B42" s="76"/>
+      <c r="C42" s="76"/>
       <c r="D42" s="32">
         <f t="shared" ref="D42:K42" si="8">IFERROR(D39/D41,0)</f>
         <v>0.14285714285714285</v>
@@ -3105,34 +3105,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="64" t="s">
         <v>38</v>
       </c>
-      <c r="B1" s="72"/>
-      <c r="C1" s="72"/>
-      <c r="D1" s="72"/>
-      <c r="E1" s="72"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="72"/>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
-      <c r="J1" s="72"/>
-      <c r="K1" s="72"/>
+      <c r="B1" s="64"/>
+      <c r="C1" s="64"/>
+      <c r="D1" s="64"/>
+      <c r="E1" s="64"/>
+      <c r="F1" s="64"/>
+      <c r="G1" s="64"/>
+      <c r="H1" s="64"/>
+      <c r="I1" s="64"/>
+      <c r="J1" s="64"/>
+      <c r="K1" s="64"/>
     </row>
     <row r="2" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="65" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
-      <c r="G2" s="66"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-      <c r="J2" s="66"/>
-      <c r="K2" s="66"/>
+      <c r="B2" s="65"/>
+      <c r="C2" s="65"/>
+      <c r="D2" s="65"/>
+      <c r="E2" s="65"/>
+      <c r="F2" s="65"/>
+      <c r="G2" s="65"/>
+      <c r="H2" s="65"/>
+      <c r="I2" s="65"/>
+      <c r="J2" s="65"/>
+      <c r="K2" s="65"/>
     </row>
     <row r="3" spans="1:11" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A3" s="37"/>
@@ -3426,15 +3426,15 @@
       <c r="H13" s="58"/>
     </row>
     <row r="14" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="73" t="s">
+      <c r="A14" s="66" t="s">
         <v>55</v>
       </c>
-      <c r="B14" s="73"/>
-      <c r="C14" s="73"/>
-      <c r="D14" s="73"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="73"/>
+      <c r="B14" s="66"/>
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66"/>
+      <c r="G14" s="66"/>
       <c r="H14" s="59"/>
       <c r="I14" s="44"/>
       <c r="J14" s="44"/>
@@ -3463,19 +3463,19 @@
       </c>
     </row>
     <row r="19" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="66" t="s">
+      <c r="A19" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="B19" s="66"/>
-      <c r="C19" s="66"/>
-      <c r="D19" s="66"/>
-      <c r="E19" s="66"/>
-      <c r="F19" s="66"/>
-      <c r="G19" s="66"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="66"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
     </row>
     <row r="20" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="37"/>
@@ -3736,94 +3736,94 @@
       </c>
     </row>
     <row r="30" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="74" t="s">
+      <c r="A30" s="67" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="74"/>
-      <c r="C30" s="74"/>
-      <c r="D30" s="74"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-      <c r="I30" s="74"/>
-      <c r="J30" s="74"/>
-      <c r="K30" s="74"/>
+      <c r="B30" s="67"/>
+      <c r="C30" s="67"/>
+      <c r="D30" s="67"/>
+      <c r="E30" s="67"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="67"/>
+      <c r="H30" s="67"/>
+      <c r="I30" s="67"/>
+      <c r="J30" s="67"/>
+      <c r="K30" s="67"/>
     </row>
     <row r="31" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="50"/>
-      <c r="B31" s="75" t="s">
+      <c r="B31" s="68" t="s">
         <v>72</v>
       </c>
-      <c r="C31" s="75"/>
-      <c r="D31" s="75"/>
-      <c r="E31" s="75"/>
-      <c r="F31" s="75"/>
-      <c r="G31" s="75"/>
-      <c r="H31" s="75"/>
-      <c r="I31" s="75"/>
-      <c r="J31" s="75"/>
-      <c r="K31" s="75"/>
+      <c r="C31" s="68"/>
+      <c r="D31" s="68"/>
+      <c r="E31" s="68"/>
+      <c r="F31" s="68"/>
+      <c r="G31" s="68"/>
+      <c r="H31" s="68"/>
+      <c r="I31" s="68"/>
+      <c r="J31" s="68"/>
+      <c r="K31" s="68"/>
     </row>
     <row r="32" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="50"/>
-      <c r="B32" s="75" t="s">
+      <c r="B32" s="68" t="s">
         <v>73</v>
       </c>
-      <c r="C32" s="75"/>
-      <c r="D32" s="75"/>
-      <c r="E32" s="75"/>
-      <c r="F32" s="75"/>
-      <c r="G32" s="75"/>
-      <c r="H32" s="75"/>
-      <c r="I32" s="75"/>
-      <c r="J32" s="75"/>
-      <c r="K32" s="75"/>
+      <c r="C32" s="68"/>
+      <c r="D32" s="68"/>
+      <c r="E32" s="68"/>
+      <c r="F32" s="68"/>
+      <c r="G32" s="68"/>
+      <c r="H32" s="68"/>
+      <c r="I32" s="68"/>
+      <c r="J32" s="68"/>
+      <c r="K32" s="68"/>
     </row>
     <row r="33" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="50"/>
-      <c r="B33" s="75" t="s">
+      <c r="B33" s="68" t="s">
         <v>74</v>
       </c>
-      <c r="C33" s="75"/>
-      <c r="D33" s="75"/>
-      <c r="E33" s="75"/>
-      <c r="F33" s="75"/>
-      <c r="G33" s="75"/>
-      <c r="H33" s="75"/>
-      <c r="I33" s="75"/>
-      <c r="J33" s="75"/>
-      <c r="K33" s="75"/>
+      <c r="C33" s="68"/>
+      <c r="D33" s="68"/>
+      <c r="E33" s="68"/>
+      <c r="F33" s="68"/>
+      <c r="G33" s="68"/>
+      <c r="H33" s="68"/>
+      <c r="I33" s="68"/>
+      <c r="J33" s="68"/>
+      <c r="K33" s="68"/>
     </row>
     <row r="34" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="50"/>
-      <c r="B34" s="75" t="s">
+      <c r="B34" s="68" t="s">
         <v>75</v>
       </c>
-      <c r="C34" s="75"/>
-      <c r="D34" s="75"/>
-      <c r="E34" s="75"/>
-      <c r="F34" s="75"/>
-      <c r="G34" s="75"/>
-      <c r="H34" s="75"/>
-      <c r="I34" s="75"/>
-      <c r="J34" s="75"/>
-      <c r="K34" s="75"/>
+      <c r="C34" s="68"/>
+      <c r="D34" s="68"/>
+      <c r="E34" s="68"/>
+      <c r="F34" s="68"/>
+      <c r="G34" s="68"/>
+      <c r="H34" s="68"/>
+      <c r="I34" s="68"/>
+      <c r="J34" s="68"/>
+      <c r="K34" s="68"/>
     </row>
     <row r="35" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="51"/>
-      <c r="B35" s="76" t="s">
+      <c r="B35" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="C35" s="76"/>
-      <c r="D35" s="76"/>
-      <c r="E35" s="76"/>
-      <c r="F35" s="76"/>
-      <c r="G35" s="76"/>
-      <c r="H35" s="76"/>
-      <c r="I35" s="76"/>
-      <c r="J35" s="76"/>
-      <c r="K35" s="76"/>
+      <c r="C35" s="69"/>
+      <c r="D35" s="69"/>
+      <c r="E35" s="69"/>
+      <c r="F35" s="69"/>
+      <c r="G35" s="69"/>
+      <c r="H35" s="69"/>
+      <c r="I35" s="69"/>
+      <c r="J35" s="69"/>
+      <c r="K35" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="10">
@@ -3941,42 +3941,42 @@
     </row>
     <row r="8" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="55" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
     </row>
     <row r="9" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="53" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="53" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="53" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="53" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="53" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="53" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" spans="2:2" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="53" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
